--- a/docs/Extra/ActiPASS-Diary-example.xlsx
+++ b/docs/Extra/ActiPASS-Diary-example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pashe866\Coding\Matlab\AMM\Ergo-Tools\ActiPASS\docs\Extra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pasan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F202A7F-BC56-44F8-A1B7-AC1BF613F0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD70E64-9871-43CD-A9F6-F926F82E4FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExampleData" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="72">
   <si>
     <t>ID</t>
   </si>
@@ -151,9 +151,6 @@
     <t xml:space="preserve">Date and time </t>
   </si>
   <si>
-    <t>Start Stop</t>
-  </si>
-  <si>
     <t>Ref</t>
   </si>
   <si>
@@ -190,9 +187,6 @@
     <t xml:space="preserve">This means that known gaps between events should also be entered in the diary with a suitable event name which defines the gap (for an example NE can be used to denote no-event). </t>
   </si>
   <si>
-    <t>Night, Bed or Bedtime</t>
-  </si>
-  <si>
     <t>Specific Event codes which give instructions to ActiPASS software</t>
   </si>
   <si>
@@ -202,9 +196,6 @@
     <t>MNW</t>
   </si>
   <si>
-    <t>The 'MNW' is a not-worn period and all activities detected in this period will ignored and will be be re-classified as NW. Can be used in special situations like accelerometer is carried in a bag, but not-worn</t>
-  </si>
-  <si>
     <t>The even name 'NE' represents 'no event' in ActiPASS terminology. It can be used to end an event where the next event is unknown. Anyway ths is not a special event, but just a suggested naming convention</t>
   </si>
   <si>
@@ -308,13 +299,185 @@
   </si>
   <si>
     <t xml:space="preserve">The event name "Ref" can be used if a reference position (Standing still upright) is used for individual calibration.  </t>
+  </si>
+  <si>
+    <t>The 'MNW' or "FNW" is a manual or forced non-wear period and all activities detected in this period will ignored and will be be re-classified as NW. Can be used in special situations like accelerometer is carried in a bag, but not-worn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">These can be used during stats generation phase to define "DayType" and also selecting an optimal 7 days of measurment automatically. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Start</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Stop</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Work</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Leisure</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Night</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bedtime</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MNW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FNW</t>
+    </r>
+  </si>
+  <si>
+    <t>Column name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Event name</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,20 +514,51 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -385,22 +579,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Heading 1" xfId="1" builtinId="16"/>
+  <cellStyles count="3">
+    <cellStyle name="60% - Accent4" xfId="1" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="2" builtinId="45"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -514,13 +712,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>95249</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>180974</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -878,18 +1076,18 @@
   <dimension ref="A1:F160"/>
   <sheetFormatPr defaultColWidth="12" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="12" style="6"/>
-    <col min="3" max="3" width="9.28515625" style="6" customWidth="1"/>
+    <col min="1" max="2" width="12" style="5"/>
+    <col min="3" max="3" width="9.28515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D1" t="s">
@@ -900,544 +1098,544 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>45</v>
+      <c r="C2" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>61</v>
+      <c r="C3" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>62</v>
+        <v>13</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>60</v>
+      <c r="C4" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>46</v>
+      <c r="C5" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>47</v>
+      <c r="C6" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>48</v>
+      <c r="A7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>49</v>
+      <c r="A8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>46</v>
+      <c r="A9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>50</v>
+      <c r="A10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>51</v>
+      <c r="A11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>47</v>
+      <c r="A12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>52</v>
+      <c r="A13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>53</v>
+      <c r="A14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>54</v>
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>49</v>
+      <c r="A16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>55</v>
+      <c r="A17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>53</v>
+      <c r="A18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>56</v>
+      <c r="A19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>57</v>
+      <c r="A20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>58</v>
+      <c r="A21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>64</v>
+      <c r="A22" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>63</v>
+      <c r="A23" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>46</v>
+      <c r="A24" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="6" t="s">
+      <c r="A25" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>48</v>
+      <c r="A26" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>49</v>
+      <c r="A27" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>46</v>
+      <c r="A28" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>50</v>
+      <c r="A29" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>51</v>
+      <c r="A30" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="6" t="s">
+      <c r="A31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>52</v>
+      <c r="A32" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>53</v>
+      <c r="A33" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>54</v>
+      <c r="A34" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>49</v>
+      <c r="A35" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>55</v>
+      <c r="A36" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>53</v>
+      <c r="A37" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>59</v>
+      <c r="A38" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>51</v>
+      <c r="A39" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>11</v>
@@ -1471,39 +1669,39 @@
       <c r="D48" s="1"/>
     </row>
     <row r="49" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C49" s="7"/>
+      <c r="C49" s="6"/>
       <c r="D49" s="3"/>
     </row>
     <row r="50" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C50" s="7"/>
+      <c r="C50" s="6"/>
       <c r="D50" s="3"/>
     </row>
     <row r="51" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C51" s="7"/>
+      <c r="C51" s="6"/>
       <c r="D51" s="3"/>
     </row>
     <row r="52" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C52" s="7"/>
+      <c r="C52" s="6"/>
       <c r="D52" s="3"/>
     </row>
     <row r="53" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C53" s="7"/>
+      <c r="C53" s="6"/>
       <c r="D53" s="3"/>
     </row>
     <row r="54" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C54" s="7"/>
+      <c r="C54" s="6"/>
       <c r="D54" s="3"/>
     </row>
     <row r="55" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C55" s="7"/>
+      <c r="C55" s="6"/>
       <c r="D55" s="3"/>
     </row>
     <row r="56" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C56" s="7"/>
+      <c r="C56" s="6"/>
       <c r="D56" s="3"/>
     </row>
     <row r="57" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C57" s="7"/>
+      <c r="C57" s="6"/>
       <c r="D57" s="3"/>
     </row>
     <row r="58" spans="3:6" x14ac:dyDescent="0.25">
@@ -1827,127 +2025,165 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.5703125" customWidth="1"/>
     <col min="9" max="9" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" s="7" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="3" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>27</v>
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="4"/>
+    </row>
+    <row r="17" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+    </row>
+    <row r="19" spans="1:14" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="B24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" t="s">
         <v>29</v>
-      </c>
-      <c r="B19" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Extra/ActiPASS-Diary-example.xlsx
+++ b/docs/Extra/ActiPASS-Diary-example.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pasan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD70E64-9871-43CD-A9F6-F926F82E4FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4EF82E-4624-428E-9D8A-CF714F4DCAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -148,9 +148,6 @@
     <t>Stop</t>
   </si>
   <si>
-    <t xml:space="preserve">Date and time </t>
-  </si>
-  <si>
     <t>Ref</t>
   </si>
   <si>
@@ -212,9 +209,6 @@
   </si>
   <si>
     <t>S-0002</t>
-  </si>
-  <si>
-    <t>Defines the start of a particular event. To avoid ambiguity use ISO date time formats (Date: YYYY-MM-DD; Time: HH:mm:ss).</t>
   </si>
   <si>
     <t>2017-06-07</t>
@@ -471,6 +465,56 @@
   </si>
   <si>
     <t>Event name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date, Time </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Columns "Date" and "Time" define the start of a particular event. To avoid ambiguity and to make sure ActiPASS read the colums correctly, use ISO date time formats (Date: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>YYYY-MM-DD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">; Time: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hh:mm:ss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1099,13 +1143,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -1113,30 +1157,30 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
@@ -1144,13 +1188,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>4</v>
@@ -1158,13 +1202,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>9</v>
@@ -1172,13 +1216,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>4</v>
@@ -1186,13 +1230,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>3</v>
@@ -1200,13 +1244,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>4</v>
@@ -1214,30 +1258,30 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>4</v>
@@ -1245,13 +1289,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>9</v>
@@ -1259,13 +1303,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>4</v>
@@ -1273,13 +1317,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>3</v>
@@ -1287,13 +1331,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>4</v>
@@ -1301,13 +1345,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>3</v>
@@ -1315,30 +1359,30 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>3</v>
@@ -1346,13 +1390,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>4</v>
@@ -1360,13 +1404,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>11</v>
@@ -1374,13 +1418,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
@@ -1388,27 +1432,27 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>3</v>
@@ -1416,13 +1460,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>43</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>4</v>
@@ -1430,13 +1474,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>9</v>
@@ -1444,13 +1488,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>4</v>
@@ -1458,13 +1502,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>3</v>
@@ -1472,13 +1516,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>43</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>4</v>
@@ -1486,30 +1530,30 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>4</v>
@@ -1517,13 +1561,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>9</v>
@@ -1531,13 +1575,13 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>4</v>
@@ -1545,13 +1589,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>3</v>
@@ -1559,13 +1603,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>4</v>
@@ -1573,13 +1617,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>3</v>
@@ -1587,13 +1631,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>4</v>
@@ -1601,13 +1645,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>3</v>
@@ -1615,13 +1659,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>4</v>
@@ -1629,13 +1673,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>11</v>
@@ -2040,31 +2084,31 @@
     <row r="2" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2072,12 +2116,12 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10"/>
       <c r="D10"/>
@@ -2085,12 +2129,12 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2098,7 +2142,7 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2106,7 +2150,7 @@
     </row>
     <row r="17" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -2124,58 +2168,58 @@
     </row>
     <row r="19" spans="1:14" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2183,7 +2227,7 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
